--- a/Docs/API_4T_Music_chia_viec.xlsx
+++ b/Docs/API_4T_Music_chia_viec.xlsx
@@ -9,9 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chia việc" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách API" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Người A" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Người B" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Danh sách API'!$A$1:$L$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'API Người A'!$A$4:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'API Người B'!$A$4:$L$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +55,17 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -92,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,11 +125,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -142,6 +161,25 @@
           <fgColor rgb="00FFEB9C"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5543,4 +5581,4738 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Danh sách API Người A cần làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Sắp theo giai đoạn. Cột Trạng thái lấy tự động từ sheet 'Danh sách API' (cập nhật trạng thái ở sheet đó). Danh sách lọc theo cột Người làm tại thời điểm tạo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Quyền</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>FR / BRL</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Bảng DB</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>API-01</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>0. Nền tảng chung</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>(middleware)</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Kết nối MySQL, cấu trúc project, định dạng lỗi chung, phân trang</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B5,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>API-02</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>0. Nền tảng chung</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>(middleware)</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Xác thực JWT và kiểm tra vai trò (guest/user/artist/admin), chặn tài khoản banned</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>FR-06, BRL-03</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L6" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B6,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>API-03</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/register</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Đăng ký tài khoản (email, user_name, mật khẩu, ngày sinh); băm mật khẩu</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>FR-01</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L7" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B7,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>API-04</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/login</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Đăng nhập, trả access token và refresh token</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L8" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B8,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>API-05</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/logout</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Đăng xuất, hủy refresh token</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>RefreshToken (mới)</t>
+        </is>
+      </c>
+      <c r="L9" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B9,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>API-06</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/refresh</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Cấp lại access token từ refresh token</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>RefreshToken (mới)</t>
+        </is>
+      </c>
+      <c r="L10" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B10,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>API-07</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/verify-email?token=</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Xác minh email qua liên kết</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>User, EmailToken (mới)</t>
+        </is>
+      </c>
+      <c r="L11" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B11,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>API-08</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/resend-verification</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Gửi lại email xác minh</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>FR-02</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>EmailToken (mới)</t>
+        </is>
+      </c>
+      <c r="L12" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B12,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>API-09</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/forgot-password</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Gửi email đặt lại mật khẩu</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>PasswordReset (mới)</t>
+        </is>
+      </c>
+      <c r="L13" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B13,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>API-10</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>1. Xác thực (Auth)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>/api/auth/reset-password</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Đặt lại mật khẩu bằng token</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>FR-04</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>PasswordReset (mới)</t>
+        </is>
+      </c>
+      <c r="L14" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B14,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>API-11</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2. Hồ sơ người dùng</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Lấy thông tin tài khoản đang đăng nhập</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>FR-05</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L15" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B15,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>API-12</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>2. Hồ sơ người dùng</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Cập nhật hồ sơ: tên hiển thị, ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>FR-05</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L16" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B16,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>API-13</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>2. Hồ sơ người dùng</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/password</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu (cần mật khẩu cũ)</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>FR-05</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L17" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B17,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>API-14</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>2. Hồ sơ người dùng</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/avatar</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Tải lên ảnh đại diện</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>FR-05</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L18" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B18,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>API-28</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách playlist của tôi</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>FR-22</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Playlist</t>
+        </is>
+      </c>
+      <c r="L19" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B19,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>API-29</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Tạo playlist</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>FR-22</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Playlist</t>
+        </is>
+      </c>
+      <c r="L20" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B20,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>API-30</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/:id</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Chi tiết playlist kèm bài hát</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>FR-22</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Playlist, Playlist_song</t>
+        </is>
+      </c>
+      <c r="L21" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B21,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>API-31</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/:id</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Đổi tên, mô tả (chỉ chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>FR-22, BRL-06</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Playlist</t>
+        </is>
+      </c>
+      <c r="L22" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B22,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>API-32</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/:id</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Xóa playlist (chỉ chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>FR-22, BRL-06</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Playlist</t>
+        </is>
+      </c>
+      <c r="L23" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B23,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>API-33</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/:id/songs</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Thêm bài vào playlist (không trùng)</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>FR-22, BRL-07</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Playlist_song</t>
+        </is>
+      </c>
+      <c r="L24" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B24,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>API-34</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/:id/songs/:songId</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Bỏ bài khỏi playlist</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>FR-22</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Playlist_song</t>
+        </is>
+      </c>
+      <c r="L25" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B25,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>API-35</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>5. Playlist</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/:id/songs/order</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Sắp xếp lại thứ tự bài</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>FR-22</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Playlist_song (thêm cột position)</t>
+        </is>
+      </c>
+      <c r="L26" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B26,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>API-36</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>6. Yêu thích và theo dõi</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id/like</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Thích bài hát</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>FR-23</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>FavoriteSong (mới)</t>
+        </is>
+      </c>
+      <c r="L27" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B27,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>API-37</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>6. Yêu thích và theo dõi</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id/like</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Bỏ thích bài hát</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>FR-23</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>FavoriteSong (mới)</t>
+        </is>
+      </c>
+      <c r="L28" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B28,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>API-38</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>6. Yêu thích và theo dõi</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/liked-songs</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách bài hát yêu thích</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>FR-23</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>FavoriteSong (mới)</t>
+        </is>
+      </c>
+      <c r="L29" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B29,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>API-39</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>6. Yêu thích và theo dõi</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>/api/artists/:id/follow</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Theo dõi nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>FR-23</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>FollowArtist (mới)</t>
+        </is>
+      </c>
+      <c r="L30" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B30,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>API-40</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>6. Yêu thích và theo dõi</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>/api/artists/:id/follow</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Bỏ theo dõi nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>FR-23</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>FollowArtist (mới)</t>
+        </is>
+      </c>
+      <c r="L31" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B31,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>API-41</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>6. Yêu thích và theo dõi</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/followed-artists</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách nghệ sĩ đang theo dõi</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>FR-23</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>FollowArtist (mới)</t>
+        </is>
+      </c>
+      <c r="L32" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B32,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>API-42</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>7. Trạng thái phát và lịch sử</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/player-state</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Lấy bài, vị trí, hàng đợi đang nghe để khôi phục</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>FR-14</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>PlayerState (mới)</t>
+        </is>
+      </c>
+      <c r="L33" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B33,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>API-43</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>7. Trạng thái phát và lịch sử</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/player-state</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Lưu bài, vị trí, hàng đợi đang nghe</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>FR-14</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>PlayerState (mới)</t>
+        </is>
+      </c>
+      <c r="L34" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B34,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>API-44</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>7. Trạng thái phát và lịch sử</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/history</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Lịch sử nghe, nghe gần đây</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>FR-24</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>ListenHistory (mới)</t>
+        </is>
+      </c>
+      <c r="L35" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B35,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>API-45</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>7. Trạng thái phát và lịch sử</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/recommendations</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Gợi ý theo thể loại và lịch sử nghe</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>FR-25</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>ListenHistory, Genre</t>
+        </is>
+      </c>
+      <c r="L36" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B36,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>API-46</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>7. Trạng thái phát và lịch sử</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>/api/radio?seedSong=&amp;seedArtist=</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Tạo danh sách phát radio từ một bài hoặc nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>FR-26</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Song, Genre</t>
+        </is>
+      </c>
+      <c r="L37" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B37,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>API-64</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>10. Tải nhạc offline</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id/download</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Kiểm tra quyền và giới hạn tải, trả liên kết tải có hạn</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>FR-40, BRL-11</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Download (mới)</t>
+        </is>
+      </c>
+      <c r="L38" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B38,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>API-65</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>10. Tải nhạc offline</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/downloads</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách bài đã tải (đồng bộ giữa thiết bị)</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>FR-41, FR-44</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>Download (mới)</t>
+        </is>
+      </c>
+      <c r="L39" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B39,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>API-66</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>10. Tải nhạc offline</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>/api/users/me/downloads/:songId</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Xóa bài khỏi danh sách đã tải</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>FR-43</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Download (mới)</t>
+        </is>
+      </c>
+      <c r="L40" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B40,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="B42" s="11">
+        <f>COUNTA(B5:B40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+      <c r="B43" s="12">
+        <f>COUNTIF(I5:I40,"1")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1 - Must</t>
+        </is>
+      </c>
+      <c r="B44" s="12">
+        <f>COUNTIFS(I5:I40,"1",J5:J40,"Must")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+      <c r="B45" s="12">
+        <f>COUNTIF(I5:I40,"2")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+      <c r="B46" s="12">
+        <f>COUNTIF(I5:I40,"3")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Đã xong</t>
+        </is>
+      </c>
+      <c r="B47" s="12">
+        <f>COUNTIF(L5:L40,"Xong")+COUNTIF(L5:L40,"Đã kiểm thử")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:L40"/>
+  <conditionalFormatting sqref="L5:L40">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>OR($L5="Xong",$L5="Đã kiểm thử")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>$L5="Đang làm"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J40">
+    <cfRule type="expression" priority="3" dxfId="6">
+      <formula>$J5="Must"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Danh sách API Người B cần làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Sắp theo giai đoạn. Cột Trạng thái lấy tự động từ sheet 'Danh sách API' (cập nhật trạng thái ở sheet đó). Danh sách lọc theo cột Người làm tại thời điểm tạo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Quyền</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>FR / BRL</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Bảng DB</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>API-15</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>3. Bài hát và phát nhạc</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách bài hát, lọc theo nghệ sĩ/album/thể loại, phân trang, sắp xếp</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>FR-20</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L5" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B5,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>API-16</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>3. Bài hát và phát nhạc</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Chi tiết bài hát (kèm nghệ sĩ, album, ảnh bìa)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>FR-21</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L6" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B6,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>API-17</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>3. Bài hát và phát nhạc</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id/stream</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Phát file nhạc, hỗ trợ HTTP Range để tua; kiểm tra quyền truy cập file</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>FR-10, BRL-12</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Song (thêm cột file_url)</t>
+        </is>
+      </c>
+      <c r="L7" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B7,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>API-18</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>3. Bài hát và phát nhạc</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id/plays</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Ghi nhận một lượt nghe (tăng lượt nghe, lưu lịch sử nếu đã đăng nhập)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>FR-24, FR-62</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>ListenHistory (mới)</t>
+        </is>
+      </c>
+      <c r="L8" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B8,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>API-20</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>/api/search?q=&amp;type=</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Tìm theo tên bài, nghệ sĩ, album, thể loại</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>FR-20</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>Song, Artist, Album, Genre</t>
+        </is>
+      </c>
+      <c r="L9" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B9,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>API-21</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>/api/artists</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>FR-21</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="L10" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B10,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>API-22</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>/api/artists/:id</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Trang nghệ sĩ (thông tin, số người theo dõi)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>FR-21</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="L11" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B11,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>API-23</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>/api/artists/:id/songs</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Bài hát của nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>FR-21</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L12" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B12,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>API-24</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>/api/artists/:id/albums</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Album của nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>FR-21</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Album</t>
+        </is>
+      </c>
+      <c r="L13" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B13,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>API-25</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>/api/albums/:id</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Chi tiết album kèm danh sách bài</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>FR-21</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Album, Song</t>
+        </is>
+      </c>
+      <c r="L14" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B14,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>API-26</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>/api/genres</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách thể loại</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>FR-20</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>Genre (mới)</t>
+        </is>
+      </c>
+      <c r="L15" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B15,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>API-27</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>4. Tìm kiếm và khám phá</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>/api/genres/:id/songs</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Bài hát theo thể loại</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>FR-20</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Genre, Song</t>
+        </is>
+      </c>
+      <c r="L16" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B16,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>API-47</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>8. Quản trị: người dùng</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/users</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách người dùng, tìm kiếm, lọc theo vai trò/trạng thái</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>FR-65</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L17" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B17,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>API-48</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>8. Quản trị: người dùng</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/users/:id/status</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Khóa (banned) hoặc mở khóa tài khoản</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>FR-65, BRL-03</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L18" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B18,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>API-49</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>8. Quản trị: người dùng</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/users/:id/role</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Đổi vai trò user/artist/admin</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>FR-65</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="L19" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B19,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>API-50</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/songs</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Thêm bài hát: tải file nhạc, ảnh bìa và thông tin</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L20" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B20,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>API-51</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/songs/:id</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Sửa thông tin bài hát, ẩn/hiện, cho phép tải</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>FR-63, BRL-11</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Song (thêm is_hidden, is_downloadable)</t>
+        </is>
+      </c>
+      <c r="L21" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B21,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>API-52</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/songs/:id</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Xóa bài hát</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L22" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B22,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>API-53</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/artists</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Thêm nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="L23" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B23,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>API-54</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/artists/:id</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Sửa nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="L24" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B24,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>API-55</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/artists/:id</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Xóa nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="L25" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B25,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>API-56</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/albums</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Thêm album</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Album</t>
+        </is>
+      </c>
+      <c r="L26" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B26,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>API-57</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/albums/:id</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Sửa album</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Album</t>
+        </is>
+      </c>
+      <c r="L27" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B27,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>API-58</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/albums/:id</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Xóa album</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Album</t>
+        </is>
+      </c>
+      <c r="L28" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B28,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>API-59</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/genres</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Thêm thể loại</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Genre (mới)</t>
+        </is>
+      </c>
+      <c r="L29" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B29,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>API-60</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/genres/:id</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Sửa thể loại</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Genre (mới)</t>
+        </is>
+      </c>
+      <c r="L30" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B30,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>API-61</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/genres/:id</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Xóa thể loại</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>FR-63</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Genre (mới)</t>
+        </is>
+      </c>
+      <c r="L31" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B31,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>API-19</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>3. Bài hát và phát nhạc</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>/api/songs/:id/lyrics</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Lấy lời bài hát có mốc thời gian</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>FR-15</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>Lyrics (mới)</t>
+        </is>
+      </c>
+      <c r="L32" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B32,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>API-62</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/songs/pending</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Danh sách bài artist gửi lên chờ duyệt</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>FR-64</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Song (thêm approval_status)</t>
+        </is>
+      </c>
+      <c r="L33" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B33,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>API-63</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>9. Quản trị: nội dung nhạc</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>/api/admin/songs/:id/approval</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Duyệt hoặc từ chối bài của artist</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>FR-64</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L34" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B34,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>API-67</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>11. Cổng nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>/api/artist/me</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Hồ sơ nghệ sĩ gắn với tài khoản</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>FR-60</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Artist (thêm user_id)</t>
+        </is>
+      </c>
+      <c r="L35" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B35,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>API-68</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>11. Cổng nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>/api/artist/me</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Cập nhật hồ sơ nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>FR-60</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="L36" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B36,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>API-69</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>11. Cổng nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>/api/artist/songs</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Artist đăng bài hát (chờ admin duyệt)</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>FR-60</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L37" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B37,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>API-70</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>11. Cổng nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>/api/artist/songs/:id</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Artist sửa bài của mình</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>FR-60</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Song</t>
+        </is>
+      </c>
+      <c r="L38" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B38,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>API-71</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>11. Cổng nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>/api/artist/albums</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Artist tạo album</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>FR-60</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>Album</t>
+        </is>
+      </c>
+      <c r="L39" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B39,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>API-72</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>11. Cổng nghệ sĩ</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>/api/artist/stats</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>Lượt nghe, thích, chia sẻ, người theo dõi</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Artist</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>FR-61</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>ListenHistory, FavoriteSong, FollowArtist</t>
+        </is>
+      </c>
+      <c r="L40" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B40,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>API-73</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>12. Thống kê và đề xuất thông minh</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>/api/charts/monthly</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Bài hát và nghệ sĩ nghe nhiều nhất theo tháng</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Khách</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>FR-62</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>ListenHistory</t>
+        </is>
+      </c>
+      <c r="L41" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B41,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>API-74</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>12. Thống kê và đề xuất thông minh</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>/api/playlists/generate</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Tạo playlist theo tâm trạng, thể loại, nghệ sĩ hoặc thời lượng</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>FR-51, FR-52, FR-53</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Could</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>Song, Genre (thêm mood)</t>
+        </is>
+      </c>
+      <c r="L42" s="8">
+        <f>IFERROR(INDEX('Danh sách API'!$L$2:$L$75,MATCH($B42,'Danh sách API'!$A$2:$A$75,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="B44" s="11">
+        <f>COUNTA(B5:B42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+      <c r="B45" s="12">
+        <f>COUNTIF(I5:I42,"1")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1 - Must</t>
+        </is>
+      </c>
+      <c r="B46" s="12">
+        <f>COUNTIFS(I5:I42,"1",J5:J42,"Must")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+      <c r="B47" s="12">
+        <f>COUNTIF(I5:I42,"2")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+      <c r="B48" s="12">
+        <f>COUNTIF(I5:I42,"3")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Đã xong</t>
+        </is>
+      </c>
+      <c r="B49" s="12">
+        <f>COUNTIF(L5:L42,"Xong")+COUNTIF(L5:L42,"Đã kiểm thử")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:L42"/>
+  <conditionalFormatting sqref="L5:L42">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>OR($L5="Xong",$L5="Đã kiểm thử")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>$L5="Đang làm"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J42">
+    <cfRule type="expression" priority="3" dxfId="6">
+      <formula>$J5="Must"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>